--- a/templates/sk/pi.xlsx
+++ b/templates/sk/pi.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6550"/>
+    <workbookView windowWidth="29400" windowHeight="14100"/>
   </bookViews>
   <sheets>
     <sheet name="Standard Invoice format" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>GUANGDONG GLOBALSINO OUTDOOR SPORTS EQUIPMENT LIMITED</t>
   </si>
@@ -44,9 +44,6 @@
     <t>PI Number:</t>
   </si>
   <si>
-    <t>ETD (Baseline Date for FOB Term):</t>
-  </si>
-  <si>
     <t>Incoterm:</t>
   </si>
   <si>
@@ -128,16 +125,13 @@
     <t>EX-FACTORY DATE</t>
   </si>
   <si>
-    <t xml:space="preserve">Sub-Total </t>
-  </si>
-  <si>
-    <t>TOTAL EXCLUDING EXCISE TAX  (USD)</t>
+    <t>CHINA</t>
+  </si>
+  <si>
+    <t>Sub-Total</t>
   </si>
   <si>
     <t>Signature:</t>
-  </si>
-  <si>
-    <t>Cindy</t>
   </si>
   <si>
     <t>Date:</t>
@@ -159,7 +153,7 @@
     <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="181" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="51">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -193,8 +187,38 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -767,7 +791,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -811,25 +835,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1042,320 +1053,320 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="41" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="42" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="40" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="14">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="15">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="16">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="17">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="33" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="39" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="40" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="41" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="42" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="40" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="36" borderId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="43" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="41" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="42" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="44" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="45" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="46" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="47" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="48" borderId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="49" borderId="19">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="43" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="41" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="42" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="44" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="45" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="46" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="18">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="47" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="48" borderId="19">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="49" borderId="20">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="21">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="48" borderId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="39" borderId="19">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="48" borderId="21">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="39" borderId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1413,6 +1424,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1420,14 +1441,18 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="179" fontId="5" fillId="2" borderId="2" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1444,25 +1469,25 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="89" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="2" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="89" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="87" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -1519,32 +1544,47 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="87" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="77" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="76" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="57" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="40" fontId="5" fillId="2" borderId="4" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="2" borderId="0" xfId="75" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="2" borderId="5" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="87" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="75" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="87" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1971,14 +2011,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.6"/>
   <cols>
     <col min="1" max="1" width="17.75" style="3" customWidth="1"/>
     <col min="2" max="2" width="13.25" style="3" customWidth="1"/>
     <col min="3" max="3" width="10.75" style="3" customWidth="1"/>
     <col min="4" max="4" width="10.25" style="3" customWidth="1"/>
-    <col min="5" max="5" width="27" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.75" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="3" customWidth="1"/>
+    <col min="6" max="6" width="28.25" style="3" customWidth="1"/>
     <col min="7" max="7" width="15.25" style="3" customWidth="1"/>
     <col min="8" max="8" width="21.25" style="3" customWidth="1"/>
     <col min="9" max="9" width="13.5" style="3" customWidth="1"/>
@@ -2060,11 +2100,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="16"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="18"/>
+      <c r="C6" s="17"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="14"/>
       <c r="H6" s="14"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
@@ -2072,252 +2111,257 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:11">
       <c r="A7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="C7" s="19"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="20"/>
-      <c r="H7" s="14"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:11">
+    <row r="8" s="1" customFormat="1" ht="27" customHeight="1" spans="1:11">
       <c r="A8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="C8" s="19"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="11"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="24"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:11">
-      <c r="A9" s="21"/>
+      <c r="A9" s="25"/>
       <c r="E9" s="12"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="24"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="27"/>
+      <c r="I9" s="28"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:11">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="28"/>
-      <c r="I10" s="24"/>
+      <c r="G10" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="31"/>
+      <c r="I10" s="19"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:11">
-      <c r="A11" s="29"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="27"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="24"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="28"/>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:11">
-      <c r="A12" s="21"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="27"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="35"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="15.95" customHeight="1" spans="1:11">
-      <c r="A13" s="21"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="26" customHeight="1" spans="1:11">
       <c r="A14" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="35" t="s">
+      <c r="G14" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="H14" s="35"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="25.5" customHeight="1" spans="1:11">
       <c r="A15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="36" t="s">
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="13" t="s">
+      <c r="G15" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="39"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="23" customHeight="1" spans="1:11">
       <c r="A16" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="44"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="G16" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="G16" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="41"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="36"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="24" customHeight="1" spans="1:11">
-      <c r="A17" s="21"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
     </row>
     <row r="18" ht="16.15" customHeight="1" spans="1:11">
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:11">
-      <c r="A19" s="43" t="s">
+      <c r="A19" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="C19" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="D19" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="44" t="s">
+      <c r="E19" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="45" t="s">
+      <c r="F19" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="46" t="s">
+      <c r="G19" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="G19" s="44" t="s">
+      <c r="H19" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="47" t="s">
+      <c r="I19" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="I19" s="48" t="s">
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:11">
+      <c r="A20" s="53" t="s">
         <v>31</v>
       </c>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="24"/>
     </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="42"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="F20" s="49" t="s">
+    <row r="21" spans="1:11">
+      <c r="A21" s="46"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="61"/>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="F22" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="50"/>
-      <c r="H20" s="51"/>
-    </row>
-    <row r="21" ht="12.25" spans="1:11">
-      <c r="A21" s="42"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="G21" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="H21" s="53"/>
-    </row>
-    <row r="22" ht="12.25" spans="1:11">
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="64"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="55"/>
-      <c r="F23" s="56" t="s">
-        <v>34</v>
-      </c>
-      <c r="G23" s="57" t="s">
-        <v>35</v>
-      </c>
-      <c r="H23" s="57"/>
+      <c r="A23" s="65"/>
+      <c r="F23" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="19"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="55"/>
-      <c r="F24" s="58" t="s">
-        <v>36</v>
-      </c>
-      <c r="G24" s="18"/>
-      <c r="H24" s="59"/>
+      <c r="A24" s="65"/>
+      <c r="F24" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="21"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="6">
